--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C9E408-6010-4608-AE9E-84637B4E92D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8620E68-184D-4E18-86AD-704D1EC6583C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="2565" windowWidth="16396" windowHeight="28275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -189,7 +189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -212,6 +212,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -434,8 +437,8 @@
   <sheetFormatPr defaultColWidth="12.53125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.3984375" customWidth="1"/>
-    <col min="2" max="2" width="19.53125" customWidth="1"/>
-    <col min="3" max="3" width="77.06640625" customWidth="1"/>
+    <col min="2" max="2" width="16.19921875" customWidth="1"/>
+    <col min="3" max="3" width="89" customWidth="1"/>
     <col min="4" max="4" width="31.73046875" customWidth="1"/>
     <col min="5" max="5" width="32.06640625" customWidth="1"/>
     <col min="6" max="6" width="26.73046875" customWidth="1"/>
@@ -507,14 +510,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+    <row r="4" spans="1:8" ht="15.4" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="10" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="3" t="s">

--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8620E68-184D-4E18-86AD-704D1EC6583C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6AD794-E179-4C60-893F-F70F8BA44927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="2565" windowWidth="16396" windowHeight="28275" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3472" yWindow="2355" windowWidth="20408" windowHeight="10193" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>string[]</t>
   </si>
@@ -64,19 +64,7 @@
     <t>SelectionDialogueIdList</t>
   </si>
   <si>
-    <t>A D 키로 좌우 이동하고 SPACE키로 점프를 하세요!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>F 키를 누르면 공격 모션이 출력됩니다!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>dialogue_mainstream_1_1_400</t>
-  </si>
-  <si>
-    <t>당근 5개를 모두 얻으면 승리합니다!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>dialogue_mainstream_1_1_100</t>
@@ -87,7 +75,26 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>토끼는 행복하지만 배가 고픕니다! (텍스트 창을 눌러서 다음으로 넘기세요!)</t>
+    <t>토끼는 행복하지만 배가 고픕니다! 토끼가 전체 맵의 모든 당근을 모을 수 있게 도와주세요!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[A / D] 키로 좌우로 이동하고 [SPACE]키로 점프를 할 수 있습니다!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>F 키를 누르면 토끼가 공격합니다!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>키보드 상단 숫자키를 누르거나 우하단 스킬 카드를 드래그&amp;드랍하면 투사체를 날리는 스킬을 사용할 수 있습니다!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_1_500</t>
+  </si>
+  <si>
+    <t>스킬은</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -512,13 +519,13 @@
     </row>
     <row r="4" spans="1:8" ht="15.4" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>12</v>
@@ -531,10 +538,10 @@
         <v>12</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>11</v>
@@ -549,13 +556,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -564,24 +571,32 @@
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>19</v>
-      </c>
       <c r="C7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A8" s="3"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
+      <c r="A8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>

--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC6AD794-E179-4C60-893F-F70F8BA44927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7D8828-318D-4B7A-8231-599E55639591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3472" yWindow="2355" windowWidth="20408" windowHeight="10193" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>string[]</t>
   </si>
@@ -75,10 +75,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>토끼는 행복하지만 배가 고픕니다! 토끼가 전체 맵의 모든 당근을 모을 수 있게 도와주세요!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>[A / D] 키로 좌우로 이동하고 [SPACE]키로 점프를 할 수 있습니다!</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -94,7 +90,26 @@
     <t>dialogue_mainstream_1_1_500</t>
   </si>
   <si>
-    <t>스킬은</t>
+    <t>스킬은 공격력의 3배의 피해를 줄 수 있습니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>토끼는 행복하지만 배가 고픕니다! 토끼가 전체 맵의 모든 당근을 모을 수 있게 도와주세요!
+[텍스트 창을 눌러 다음 대사를 출력하세요</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_1_600</t>
+  </si>
+  <si>
+    <t>dialogue_mainstream_1_1_700</t>
+  </si>
+  <si>
+    <t>맵 어딘가에 숨겨진 포탈을 통해 다음 맵으로 이동할 수 있습니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>그럼 행운을 빕니다!</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -525,7 +540,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>12</v>
@@ -541,7 +556,7 @@
         <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>11</v>
@@ -559,7 +574,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>14</v>
@@ -577,10 +592,10 @@
         <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -589,34 +604,50 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="5"/>
+        <v>21</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A9" s="3"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
+      <c r="A9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A10" s="3"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
+      <c r="A10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>26</v>
+      </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>

--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F7D8828-318D-4B7A-8231-599E55639591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBA7478-0070-43FF-988C-53809C12AC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3472" yWindow="2355" windowWidth="20408" windowHeight="10193" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94,11 +94,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>토끼는 행복하지만 배가 고픕니다! 토끼가 전체 맵의 모든 당근을 모을 수 있게 도와주세요!
-[텍스트 창을 눌러 다음 대사를 출력하세요</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>dialogue_mainstream_1_1_600</t>
   </si>
   <si>
@@ -110,6 +105,11 @@
   </si>
   <si>
     <t>그럼 행운을 빕니다!</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>토끼는 행복하지만 배가 고픕니다! 토끼가 전체 맵의 모든 당근을 모을 수 있게 도와주세요!
+[텍스트 창을 눌러 다음 대사를 출력하세요.]</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -540,7 +540,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>12</v>
@@ -613,7 +613,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -622,16 +622,16 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -640,13 +640,13 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>

--- a/JsonConverter/ExcelFiles/DNDialogue.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogue.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EBA7478-0070-43FF-988C-53809C12AC5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C899E3B1-5340-49B6-88B8-DCAFF5AF8E67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3472" yWindow="2355" windowWidth="20408" windowHeight="10193" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -75,18 +75,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>[A / D] 키로 좌우로 이동하고 [SPACE]키로 점프를 할 수 있습니다!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>F 키를 누르면 토끼가 공격합니다!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>키보드 상단 숫자키를 누르거나 우하단 스킬 카드를 드래그&amp;드랍하면 투사체를 날리는 스킬을 사용할 수 있습니다!</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>dialogue_mainstream_1_1_500</t>
   </si>
   <si>
@@ -108,8 +96,21 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>토끼는 행복하지만 배가 고픕니다! 토끼가 전체 맵의 모든 당근을 모을 수 있게 도와주세요!
+    <t>토끼는 행복하지만 배가 고픕니다! 토끼 당근을 모두 모을 수 있게 도와주세요!
+맵은 3개이며 각 맵마다 5개의 당근이 있습니다.
 [텍스트 창을 눌러 다음 대사를 출력하세요.]</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>[A / D] 키로 좌우로 이동하고 [SPACE]키로 점프를 할 수 있습니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>F 키를 누르면 토끼가 공격합니다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>키보드 상단 숫자키를 누르거나 우하단 스킬 카드를 드래그&amp;드랍하면 투사체를 날리는 스킬을 사용할 수 있습니다.</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -540,7 +541,7 @@
         <v>16</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>12</v>
@@ -556,7 +557,7 @@
         <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>11</v>
@@ -574,7 +575,7 @@
         <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>14</v>
@@ -592,10 +593,10 @@
         <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -604,16 +605,16 @@
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -622,16 +623,16 @@
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -640,13 +641,13 @@
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
